--- a/04_beispiel_mit_simulierten_survival_data/parameters_simulation_shape_1.xlsb.xlsx
+++ b/04_beispiel_mit_simulierten_survival_data/parameters_simulation_shape_1.xlsb.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rehan\meine_Repos\Masterarbeit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rehan\meine_Repos\Masterarbeit\04_beispiel_mit_simulierten_survival_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE06057-BD24-4960-B683-D2695BA2BF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D793E9E5-76EE-47C7-B1FE-5C79E0EC2271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-18120" yWindow="-4980" windowWidth="18240" windowHeight="28320" activeTab="1" xr2:uid="{A9158FE8-4C15-45A2-AFBE-76AC3C37AE55}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
     <t>cens_rate</t>
   </si>
@@ -216,6 +216,14 @@
   </si>
   <si>
     <t xml:space="preserve">n   = </t>
+  </si>
+  <si>
+    <t>tau = 37
+params_data_creation =                  { 'shape_weibull': 1, 
+                        'scale_weibull_base': 9115.851814783131        , 
+                        'rate_censoring':  0.04021055606963396   ,
+                        'b_bloodp': -0.405, 'b_diab': -0.4, 'b_age': -0.05, 'b_bmi': -0.01, 'b_kreat': -0.2, 
+                        'n': n, 'seed': seed, 'tau': tau}</t>
   </si>
 </sst>
 </file>
@@ -1294,13 +1302,13 @@
         <v>69.930000000000007</v>
       </c>
     </row>
-    <row r="26" spans="3:8" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:8" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C26" s="5"/>
       <c r="D26" s="16">
         <v>40</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F26" s="19">
         <f>$F$22*D26/100</f>
